--- a/Excel/ProfileTestData.xlsx
+++ b/Excel/ProfileTestData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24026"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\doantotnghiep\Unit test\Realtime-Auction-Test\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\đồ án\Test unit\TestProject1\Realtime-Auction-test\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F6DCB67-51FB-4AA2-B153-410C6F7CF8BB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3E9D28-3B68-4C34-96D7-4935EE825E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ThongTinCaNhan" sheetId="1" r:id="rId1"/>
@@ -18,11 +18,6 @@
     <sheet name="HuongDan" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
-  <extLst>
-    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
-      <xlwcv:version setVersion="1"/>
-    </ext>
-  </extLst>
 </workbook>
 </file>
 
@@ -415,37 +410,37 @@
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <sz val="10"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
       <b/>
       <sz val="12"/>
       <color rgb="FFC55A11"/>
       <name val="Arial"/>
+      <family val="2"/>
     </font>
     <font>
-      <sz val="10"/>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Arial"/>
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC55A11"/>
-      </patternFill>
-    </fill>
   </fills>
-  <borders count="2">
+  <borders count="1">
     <border>
       <left/>
       <right/>
@@ -453,36 +448,24 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFBFBFBF"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFBFBFBF"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFBFBFBF"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFBFBFBF"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment vertical="top" wrapText="1"/>
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="11" fontId="4" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="11" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -788,364 +771,364 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11" customWidth="1"/>
+    <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="26" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
-    <col min="6" max="6" width="14" customWidth="1"/>
+    <col min="6" max="6" width="17.33203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.25">
-      <c r="A1" s="1" t="s">
+    <row r="1" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="1" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="1" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="5" t="s">
         <v>3</v>
       </c>
-      <c r="E1" s="1" t="s">
+      <c r="E1" s="5" t="s">
         <v>4</v>
       </c>
-      <c r="F1" s="1" t="s">
+      <c r="F1" s="5" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>7</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E2" s="4"/>
-      <c r="F2" s="4" t="s">
+      <c r="E2" s="2"/>
+      <c r="F2" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E3" s="4"/>
-      <c r="F3" s="4" t="s">
+      <c r="E3" s="2"/>
+      <c r="F3" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="C4" s="4" t="s">
+      <c r="C4" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D4" s="4" t="s">
+      <c r="D4" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="E4" s="4"/>
-      <c r="F4" s="4" t="s">
+      <c r="E4" s="2"/>
+      <c r="F4" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E5" s="4"/>
-      <c r="F5" s="4" t="s">
+      <c r="E5" s="2"/>
+      <c r="F5" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="4"/>
-      <c r="D6" s="4" t="s">
+      <c r="C6" s="2"/>
+      <c r="D6" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="E6" s="2"/>
+      <c r="F6" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>23</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="D7" s="4" t="s">
+      <c r="D7" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="E7" s="2"/>
+      <c r="F7" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>28</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E8" s="4"/>
-      <c r="F8" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="E8" s="2"/>
+      <c r="F8" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>31</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E9" s="4"/>
-      <c r="F9" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="E9" s="2"/>
+      <c r="F9" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>32</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E10" s="4"/>
-      <c r="F10" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="E10" s="2"/>
+      <c r="F10" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>35</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="2" t="s">
         <v>37</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="E11" s="4"/>
-      <c r="F11" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="E11" s="2"/>
+      <c r="F11" s="2" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D12" s="4"/>
-      <c r="E12" s="4"/>
-      <c r="F12" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="D12" s="2"/>
+      <c r="E12" s="2"/>
+      <c r="F12" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E13" s="4"/>
-      <c r="F13" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="E13" s="2"/>
+      <c r="F13" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>43</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="E14" s="4"/>
-      <c r="F14" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="E14" s="2"/>
+      <c r="F14" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="2" t="s">
         <v>47</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D15" s="5">
+      <c r="D15" s="6">
         <v>9.9999999999999908E+189</v>
       </c>
-      <c r="E15" s="4"/>
-      <c r="F15" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="E15" s="2"/>
+      <c r="F15" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>48</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="2" t="s">
         <v>49</v>
       </c>
-      <c r="C16" s="4" t="s">
+      <c r="C16" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="4" t="s">
+      <c r="D16" s="2" t="s">
         <v>50</v>
       </c>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="E16" s="2"/>
+      <c r="F16" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="2" t="s">
         <v>53</v>
       </c>
-      <c r="E17" s="4"/>
-      <c r="F17" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" s="4" t="s">
+      <c r="E17" s="2"/>
+      <c r="F17" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="2" t="s">
         <v>54</v>
       </c>
-      <c r="B18" s="4" t="s">
+      <c r="B18" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C18" s="4" t="s">
+      <c r="C18" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D18" s="4" t="s">
+      <c r="D18" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="E18" s="4"/>
-      <c r="F18" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" s="4" t="s">
+      <c r="E18" s="2"/>
+      <c r="F18" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="B19" s="4" t="s">
+      <c r="B19" s="2" t="s">
         <v>58</v>
       </c>
-      <c r="C19" s="4" t="s">
+      <c r="C19" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="D19" s="4" t="s">
+      <c r="D19" s="2" t="s">
         <v>59</v>
       </c>
-      <c r="E19" s="4"/>
-      <c r="F19" s="4" t="s">
+      <c r="E19" s="2"/>
+      <c r="F19" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A20" s="4" t="s">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="B20" s="4" t="s">
+      <c r="B20" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="F20" s="4" t="s">
+      <c r="F20" s="2" t="s">
         <v>10</v>
       </c>
     </row>
@@ -1157,7 +1140,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -1167,7 +1150,7 @@
     <col min="7" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1190,325 +1173,325 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="4" t="s">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="2" t="s">
         <v>63</v>
       </c>
-      <c r="B2" s="4" t="s">
+      <c r="B2" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C2" s="4" t="s">
+      <c r="C2" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D2" s="4" t="s">
+      <c r="D2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="E2" s="4" t="s">
+      <c r="E2" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="F2" s="4"/>
-      <c r="G2" s="4" t="s">
+      <c r="F2" s="2"/>
+      <c r="G2" s="2" t="s">
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="4" t="s">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="B3" s="4" t="s">
+      <c r="B3" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C3" s="4" t="s">
+      <c r="C3" s="2" t="s">
         <v>69</v>
       </c>
-      <c r="D3" s="4" t="s">
+      <c r="D3" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E3" s="4" t="s">
+      <c r="E3" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F3" s="4"/>
-      <c r="G3" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="4" t="s">
+      <c r="F3" s="2"/>
+      <c r="G3" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="2" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="4" t="s">
+      <c r="B4" s="2" t="s">
         <v>72</v>
       </c>
-      <c r="C4" s="4"/>
-      <c r="D4" s="4" t="s">
+      <c r="C4" s="2"/>
+      <c r="D4" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E4" s="4" t="s">
+      <c r="E4" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="F4" s="4"/>
-      <c r="G4" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="4" t="s">
+      <c r="F4" s="2"/>
+      <c r="G4" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="2" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="4" t="s">
+      <c r="B5" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C5" s="4" t="s">
+      <c r="C5" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D5" s="4" t="s">
+      <c r="D5" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E5" s="4" t="s">
+      <c r="E5" s="2" t="s">
         <v>75</v>
       </c>
-      <c r="F5" s="4"/>
-      <c r="G5" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="4" t="s">
+      <c r="F5" s="2"/>
+      <c r="G5" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="B6" s="4" t="s">
+      <c r="B6" s="2" t="s">
         <v>77</v>
       </c>
-      <c r="C6" s="4" t="s">
+      <c r="C6" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="4" t="s">
+      <c r="D6" s="2" t="s">
         <v>70</v>
       </c>
-      <c r="E6" s="4"/>
-      <c r="F6" s="4"/>
-      <c r="G6" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="4" t="s">
+      <c r="E6" s="2"/>
+      <c r="F6" s="2"/>
+      <c r="G6" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="2" t="s">
         <v>78</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="2" t="s">
         <v>79</v>
       </c>
-      <c r="C7" s="4" t="s">
+      <c r="C7" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
-      <c r="F7" s="4"/>
-      <c r="G7" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="4" t="s">
+      <c r="D7" s="2"/>
+      <c r="E7" s="2"/>
+      <c r="F7" s="2"/>
+      <c r="G7" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="B8" s="4" t="s">
+      <c r="B8" s="2" t="s">
         <v>81</v>
       </c>
-      <c r="C8" s="4" t="s">
+      <c r="C8" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D8" s="4" t="s">
+      <c r="D8" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="E8" s="4" t="s">
+      <c r="E8" s="2" t="s">
         <v>82</v>
       </c>
-      <c r="F8" s="4"/>
-      <c r="G8" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="4" t="s">
+      <c r="F8" s="2"/>
+      <c r="G8" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="2" t="s">
         <v>83</v>
       </c>
-      <c r="B9" s="4" t="s">
+      <c r="B9" s="2" t="s">
         <v>84</v>
       </c>
-      <c r="C9" s="4" t="s">
+      <c r="C9" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="4" t="s">
+      <c r="D9" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="E9" s="4" t="s">
+      <c r="E9" s="2" t="s">
         <v>85</v>
       </c>
-      <c r="F9" s="4"/>
-      <c r="G9" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="4" t="s">
+      <c r="F9" s="2"/>
+      <c r="G9" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="2" t="s">
         <v>86</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>87</v>
       </c>
-      <c r="C10" s="4" t="s">
+      <c r="C10" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D10" s="4" t="s">
+      <c r="D10" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="E10" s="4" t="s">
+      <c r="E10" s="2" t="s">
         <v>88</v>
       </c>
-      <c r="F10" s="4"/>
-      <c r="G10" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="4" t="s">
+      <c r="F10" s="2"/>
+      <c r="G10" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="2" t="s">
         <v>89</v>
       </c>
-      <c r="B11" s="4" t="s">
+      <c r="B11" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C11" s="4" t="s">
+      <c r="C11" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D11" s="4" t="s">
+      <c r="D11" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="E11" s="4" t="s">
+      <c r="E11" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="F11" s="4"/>
-      <c r="G11" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="4" t="s">
+      <c r="F11" s="2"/>
+      <c r="G11" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="B12" s="4" t="s">
+      <c r="B12" s="2" t="s">
         <v>93</v>
       </c>
-      <c r="C12" s="4" t="s">
+      <c r="C12" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="4" t="s">
+      <c r="D12" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="E12" s="4" t="s">
+      <c r="E12" s="2" t="s">
         <v>94</v>
       </c>
-      <c r="F12" s="4"/>
-      <c r="G12" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="4" t="s">
+      <c r="F12" s="2"/>
+      <c r="G12" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="2" t="s">
         <v>95</v>
       </c>
-      <c r="B13" s="4" t="s">
+      <c r="B13" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="E13" s="4" t="s">
+      <c r="E13" s="2" t="s">
         <v>97</v>
       </c>
-      <c r="F13" s="4"/>
-      <c r="G13" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="4" t="s">
+      <c r="F13" s="2"/>
+      <c r="G13" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="2" t="s">
         <v>98</v>
       </c>
-      <c r="B14" s="4" t="s">
+      <c r="B14" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="E14" s="4" t="s">
+      <c r="E14" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="F14" s="4"/>
-      <c r="G14" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="4" t="s">
+      <c r="F14" s="2"/>
+      <c r="G14" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="B15" s="4" t="s">
+      <c r="B15" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="C15" s="4" t="s">
+      <c r="C15" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D15" s="4" t="s">
+      <c r="D15" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="E15" s="4" t="s">
+      <c r="E15" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="F15" s="4"/>
-      <c r="G15" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="4" t="s">
+      <c r="F15" s="2"/>
+      <c r="G15" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="B16" s="4" t="s">
+      <c r="B16" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="C16" s="4"/>
-      <c r="D16" s="4"/>
-      <c r="E16" s="4"/>
-      <c r="F16" s="4"/>
-      <c r="G16" s="4" t="s">
-        <v>22</v>
-      </c>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="4" t="s">
+      <c r="C16" s="2"/>
+      <c r="D16" s="2"/>
+      <c r="E16" s="2"/>
+      <c r="F16" s="2"/>
+      <c r="G16" s="2" t="s">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="2" t="s">
         <v>105</v>
       </c>
-      <c r="B17" s="4" t="s">
+      <c r="B17" s="2" t="s">
         <v>106</v>
       </c>
-      <c r="C17" s="4" t="s">
+      <c r="C17" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D17" s="4" t="s">
+      <c r="D17" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="E17" s="4" t="s">
+      <c r="E17" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="F17" s="4"/>
-      <c r="G17" s="4" t="s">
+      <c r="F17" s="2"/>
+      <c r="G17" s="2" t="s">
         <v>22</v>
       </c>
     </row>
@@ -1520,82 +1503,82 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A16"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A1" s="2" t="s">
+    <row r="1" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A1" s="3" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="3"/>
-    </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="3" t="s">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="4"/>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="3" t="s">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="3" t="s">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="3" t="s">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="3"/>
-    </row>
-    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A8" s="2" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="4"/>
+    </row>
+    <row r="8" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A8" s="3" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="3" t="s">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="3" t="s">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="4" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="3" t="s">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="4" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="3" t="s">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="4" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="3" t="s">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="3"/>
-    </row>
-    <row r="15" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="A15" s="2" t="s">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="4"/>
+    </row>
+    <row r="15" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+      <c r="A15" s="3" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="3" t="s">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="4" t="s">
         <v>120</v>
       </c>
     </row>

--- a/Excel/ProfileTestData.xlsx
+++ b/Excel/ProfileTestData.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24026"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27932"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\đồ án\Test unit\TestProject1\Realtime-Auction-test\Excel\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\doantotnghiep\Unit test\Realtime-Auction-Test\Excel\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0D3E9D28-3B68-4C34-96D7-4935EE825E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6D3F097C-D13C-493F-85A3-52B01E051FE6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="ThongTinCaNhan" sheetId="1" r:id="rId1"/>
@@ -18,6 +18,11 @@
     <sheet name="HuongDan" sheetId="3" r:id="rId3"/>
   </sheets>
   <calcPr calcId="0"/>
+  <extLst>
+    <ext xmlns:xlwcv="http://schemas.microsoft.com/office/spreadsheetml/2024/workbookCompatibilityVersion" uri="{D14903EA-33C4-47F7-8F05-3474C54BE107}">
+      <xlwcv:version setVersion="1"/>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -771,17 +776,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:F20"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="17" customWidth="1"/>
     <col min="2" max="2" width="34" customWidth="1"/>
     <col min="3" max="3" width="26" customWidth="1"/>
     <col min="4" max="4" width="18" customWidth="1"/>
     <col min="5" max="5" width="38" customWidth="1"/>
-    <col min="6" max="6" width="17.33203125" customWidth="1"/>
+    <col min="6" max="6" width="17.28515625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -801,7 +806,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>6</v>
       </c>
@@ -819,7 +824,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>11</v>
       </c>
@@ -837,7 +842,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>14</v>
       </c>
@@ -855,7 +860,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>17</v>
       </c>
@@ -873,7 +878,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>20</v>
       </c>
@@ -889,7 +894,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>23</v>
       </c>
@@ -907,7 +912,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>26</v>
       </c>
@@ -922,10 +927,10 @@
       </c>
       <c r="E8" s="2"/>
       <c r="F8" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>29</v>
       </c>
@@ -940,10 +945,10 @@
       </c>
       <c r="E9" s="2"/>
       <c r="F9" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>32</v>
       </c>
@@ -958,10 +963,10 @@
       </c>
       <c r="E10" s="2"/>
       <c r="F10" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" ht="39.6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" ht="38.25" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>35</v>
       </c>
@@ -976,10 +981,10 @@
       </c>
       <c r="E11" s="2"/>
       <c r="F11" s="2" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+        <v>22</v>
+      </c>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>38</v>
       </c>
@@ -995,7 +1000,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>40</v>
       </c>
@@ -1013,7 +1018,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>43</v>
       </c>
@@ -1031,7 +1036,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:6" ht="77.400000000000006" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" ht="77.45" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>46</v>
       </c>
@@ -1049,7 +1054,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>48</v>
       </c>
@@ -1067,7 +1072,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>51</v>
       </c>
@@ -1085,7 +1090,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>54</v>
       </c>
@@ -1103,7 +1108,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>57</v>
       </c>
@@ -1121,7 +1126,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>121</v>
       </c>
@@ -1140,7 +1145,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:G17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
     <col min="2" max="2" width="38" customWidth="1"/>
@@ -1150,7 +1155,7 @@
     <col min="7" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="27.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" ht="30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1173,7 +1178,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>63</v>
       </c>
@@ -1194,7 +1199,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>67</v>
       </c>
@@ -1215,7 +1220,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>71</v>
       </c>
@@ -1234,7 +1239,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>73</v>
       </c>
@@ -1255,7 +1260,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>76</v>
       </c>
@@ -1274,7 +1279,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>78</v>
       </c>
@@ -1291,7 +1296,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>80</v>
       </c>
@@ -1312,7 +1317,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>83</v>
       </c>
@@ -1333,7 +1338,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>86</v>
       </c>
@@ -1354,7 +1359,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>89</v>
       </c>
@@ -1375,7 +1380,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>92</v>
       </c>
@@ -1396,7 +1401,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>95</v>
       </c>
@@ -1417,7 +1422,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>98</v>
       </c>
@@ -1438,7 +1443,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>101</v>
       </c>
@@ -1459,7 +1464,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>103</v>
       </c>
@@ -1474,7 +1479,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>105</v>
       </c>
@@ -1503,81 +1508,81 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:A16"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="110" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A1" s="3" t="s">
         <v>108</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="4"/>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>109</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>110</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="4" t="s">
         <v>111</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="4" t="s">
         <v>112</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="4"/>
     </row>
-    <row r="8" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A8" s="3" t="s">
         <v>113</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="4" t="s">
         <v>114</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="4" t="s">
         <v>115</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="4" t="s">
         <v>116</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="4" t="s">
         <v>117</v>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="4" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="4"/>
     </row>
-    <row r="15" spans="1:1" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A15" s="3" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="4" t="s">
         <v>120</v>
       </c>
